--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB09729-29A4-41B7-B0D4-EBEE1F613DE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D07D741-CF80-445E-B2FD-A45166776CF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t>Join Comp</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Result set mid round</t>
   </si>
   <si>
-    <t>MOBILE NOTIFICATION</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -106,6 +103,15 @@
   </si>
   <si>
     <t>Game started</t>
+  </si>
+  <si>
+    <t>BUILT</t>
+  </si>
+  <si>
+    <t>MOBILE NOTIFICATION (pending)</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -170,12 +176,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -492,18 +501,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:E17"/>
+  <dimension ref="B2:F17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -512,10 +521,13 @@
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -525,11 +537,11 @@
       <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -540,10 +552,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -553,8 +568,11 @@
       <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
@@ -564,8 +582,11 @@
       <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
@@ -575,8 +596,11 @@
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -586,8 +610,11 @@
       <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
@@ -597,8 +624,11 @@
       <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -608,8 +638,11 @@
       <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
@@ -619,8 +652,11 @@
       <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -630,8 +666,11 @@
       <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
@@ -641,8 +680,11 @@
       <c r="D13" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
@@ -652,8 +694,11 @@
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
@@ -663,8 +708,11 @@
       <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
@@ -672,13 +720,13 @@
         <v>18</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
@@ -686,10 +734,10 @@
         <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20367"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D07D741-CF80-445E-B2FD-A45166776CF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DED0F6-BDA2-4A26-9FB6-4495CC1855CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
   <si>
     <t>Join Comp</t>
   </si>
@@ -205,9 +208,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -245,7 +248,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -351,7 +354,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -493,7 +496,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -708,6 +711,9 @@
       <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="E15" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="F15" s="3" t="s">
         <v>28</v>
       </c>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DED0F6-BDA2-4A26-9FB6-4495CC1855CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFB754A-1FAA-4B34-BDD3-A5FFE4F0BB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Join Comp</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>Organiser Game Invite</t>
   </si>
   <si>
     <t>CONSUMER</t>
@@ -504,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:F17"/>
+  <dimension ref="B2:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
@@ -515,7 +512,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -524,10 +521,10 @@
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
@@ -572,7 +569,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
@@ -586,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
@@ -600,7 +597,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
@@ -614,7 +611,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -628,7 +625,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
@@ -642,7 +639,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
@@ -656,7 +653,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
@@ -670,7 +667,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
@@ -684,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
@@ -697,8 +694,11 @@
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="E14" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
@@ -715,7 +715,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
@@ -726,23 +726,9 @@
         <v>18</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFB754A-1FAA-4B34-BDD3-A5FFE4F0BB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809DC25D-679D-4387-82D6-1F4F0BFEB55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
-  <si>
-    <t>Join Comp</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
   <si>
     <t>Round Over</t>
   </si>
@@ -57,54 +54,27 @@
     <t>Game Start reminder</t>
   </si>
   <si>
-    <t>Tips</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
-    <t>Official game invite</t>
-  </si>
-  <si>
-    <t>News</t>
-  </si>
-  <si>
-    <t>Created Comp</t>
-  </si>
-  <si>
-    <t>Join LMS</t>
-  </si>
-  <si>
     <t>SECTION</t>
   </si>
   <si>
     <t>EMAIL</t>
   </si>
   <si>
-    <t>Welcome</t>
-  </si>
-  <si>
     <t>Game</t>
   </si>
   <si>
     <t>Info</t>
   </si>
   <si>
-    <t>Promote competition</t>
-  </si>
-  <si>
-    <t>Result set mid round</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>CONSUMER</t>
   </si>
   <si>
-    <t>Game started</t>
-  </si>
-  <si>
     <t>BUILT</t>
   </si>
   <si>
@@ -112,6 +82,33 @@
   </si>
   <si>
     <t>--</t>
+  </si>
+  <si>
+    <t>Welcome Join Comp</t>
+  </si>
+  <si>
+    <t>Welcome Created Comp</t>
+  </si>
+  <si>
+    <t>Welcome Join LMS</t>
+  </si>
+  <si>
+    <t>Broadcast from Admin</t>
+  </si>
+  <si>
+    <t>Broadcast from Organiser</t>
+  </si>
+  <si>
+    <t>Game Members</t>
+  </si>
+  <si>
+    <t>BROADCAST</t>
+  </si>
+  <si>
+    <t>Hint - Promote competition</t>
+  </si>
+  <si>
+    <t>Hint - Result set mid round</t>
   </si>
 </sst>
 </file>
@@ -135,7 +132,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,6 +142,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -176,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -187,6 +190,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,232 +511,242 @@
   <dimension ref="B2:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="32.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809DC25D-679D-4387-82D6-1F4F0BFEB55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8CF077-792F-4EA3-8366-D2848ADBB8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="27">
   <si>
     <t>Round Over</t>
   </si>
@@ -132,7 +132,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,12 +142,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -179,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -190,10 +184,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,6 +534,9 @@
       <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
@@ -643,6 +636,9 @@
       <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F9" s="3" t="s">
         <v>17</v>
       </c>
@@ -657,6 +653,9 @@
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F10" s="3" t="s">
         <v>17</v>
       </c>
@@ -716,10 +715,10 @@
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="4"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8CF077-792F-4EA3-8366-D2848ADBB8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E636F24-1B52-4543-B860-F28240DFB26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Round Over</t>
   </si>
@@ -94,12 +94,6 @@
   </si>
   <si>
     <t>Broadcast from Admin</t>
-  </si>
-  <si>
-    <t>Broadcast from Organiser</t>
-  </si>
-  <si>
-    <t>Game Members</t>
   </si>
   <si>
     <t>BROADCAST</t>
@@ -173,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -182,6 +176,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -498,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
@@ -634,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>13</v>
@@ -651,7 +648,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>13</v>
@@ -713,7 +710,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -730,21 +727,10 @@
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="E15" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F15" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="3" t="s">
         <v>17</v>
       </c>
     </row>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E636F24-1B52-4543-B860-F28240DFB26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C548DC71-4D62-4BFC-A8E0-CDB7F8EEA789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Round Over</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Hint - Result set mid round</t>
+  </si>
+  <si>
+    <t>Share reminder</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
@@ -659,13 +662,13 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
@@ -676,13 +679,13 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
@@ -693,44 +696,61 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+      <c r="E14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="E16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>17</v>
       </c>
     </row>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C548DC71-4D62-4BFC-A8E0-CDB7F8EEA789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F44D292-2BFB-4AED-BA95-0C25EC468705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
   <si>
     <t>Round Over</t>
   </si>
@@ -534,9 +534,7 @@
       <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
@@ -551,9 +549,7 @@
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
@@ -568,9 +564,7 @@
       <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
@@ -585,9 +579,7 @@
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
@@ -602,9 +594,7 @@
       <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="3" t="s">
         <v>17</v>
       </c>
@@ -619,9 +609,7 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="3" t="s">
         <v>17</v>
       </c>
@@ -636,9 +624,7 @@
       <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="3" t="s">
         <v>17</v>
       </c>
@@ -653,9 +639,7 @@
       <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="3" t="s">
         <v>17</v>
       </c>
@@ -670,9 +654,7 @@
       <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="3" t="s">
         <v>17</v>
       </c>
@@ -747,9 +729,7 @@
       <c r="D16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="3" t="s">
         <v>17</v>
       </c>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F44D292-2BFB-4AED-BA95-0C25EC468705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDF3F07-066C-455D-BC3E-9EC90652AF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
   <si>
     <t>Round Over</t>
   </si>
@@ -534,7 +534,9 @@
       <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
@@ -549,7 +551,9 @@
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
@@ -564,7 +568,9 @@
       <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
@@ -579,7 +585,9 @@
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
@@ -594,7 +602,9 @@
       <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F7" s="3" t="s">
         <v>17</v>
       </c>
@@ -609,7 +619,9 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F8" s="3" t="s">
         <v>17</v>
       </c>
@@ -624,7 +636,9 @@
       <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F9" s="3" t="s">
         <v>17</v>
       </c>
@@ -639,7 +653,9 @@
       <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F10" s="3" t="s">
         <v>17</v>
       </c>
@@ -654,7 +670,9 @@
       <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F11" s="3" t="s">
         <v>17</v>
       </c>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDF3F07-066C-455D-BC3E-9EC90652AF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0469A970-3C54-48EB-9BB5-80C3A89BE2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Round Over</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>Hint - Result set mid round</t>
-  </si>
-  <si>
-    <t>Share reminder</t>
   </si>
 </sst>
 </file>
@@ -498,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
@@ -662,13 +659,13 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
@@ -679,13 +676,13 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
@@ -696,13 +693,13 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>13</v>
@@ -712,43 +709,26 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="3" t="s">
+      <c r="E15" s="4"/>
+      <c r="F15" s="3" t="s">
         <v>17</v>
       </c>
     </row>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0469A970-3C54-48EB-9BB5-80C3A89BE2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11E8447-709B-49A3-9E8D-622664D29C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Round Over</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Fixture reminder</t>
-  </si>
-  <si>
-    <t>Game Start reminder</t>
   </si>
   <si>
     <t>All</t>
@@ -495,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
@@ -506,19 +503,19 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
@@ -526,16 +523,16 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
@@ -543,16 +540,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
@@ -560,16 +557,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
@@ -577,16 +574,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
@@ -594,16 +591,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
@@ -614,13 +611,13 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -628,108 +625,91 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="3" t="s">
-        <v>17</v>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11E8447-709B-49A3-9E8D-622664D29C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBD7F33-645B-4E05-B2BE-745FAD5DE8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Round Over</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Hint - Result set mid round</t>
+  </si>
+  <si>
+    <t>Nudge after join and quiet</t>
   </si>
 </sst>
 </file>
@@ -492,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D174EA-1CB0-4AAB-99E9-FB17E825ADF7}">
-  <dimension ref="B2:F14"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
@@ -679,36 +682,53 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="3" t="s">
+      <c r="E15" s="4"/>
+      <c r="F15" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/email/email-outline.xlsx
+++ b/docs/email/email-outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lmslocal\docs\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBD7F33-645B-4E05-B2BE-745FAD5DE8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDE45D1-BCA0-4F98-9127-730CD6DB8318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AC65AE-6C17-448A-A5A6-78B888B68FDF}"/>
   </bookViews>
@@ -102,7 +102,7 @@
     <t>Hint - Result set mid round</t>
   </si>
   <si>
-    <t>Nudge after join and quiet</t>
+    <t>Empty competition</t>
   </si>
 </sst>
 </file>
@@ -676,7 +676,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
